--- a/artfynd/A 12829-2026 artfynd.xlsx
+++ b/artfynd/A 12829-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131706815</v>
       </c>
       <c r="B2" t="n">
-        <v>58078</v>
+        <v>58080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>131706820</v>
       </c>
       <c r="B3" t="n">
-        <v>58107</v>
+        <v>58109</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>132224249</v>
       </c>
       <c r="B7" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1699,37 +1699,43 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132224217</v>
+        <v>132224230</v>
       </c>
       <c r="B11" t="n">
-        <v>91910</v>
+        <v>8455</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1737,10 +1743,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461221</v>
+        <v>461181</v>
       </c>
       <c r="R11" t="n">
-        <v>6776620</v>
+        <v>6776732</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1800,43 +1806,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132224230</v>
+        <v>132224217</v>
       </c>
       <c r="B12" t="n">
-        <v>8455</v>
+        <v>91913</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1844,10 +1844,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461181</v>
+        <v>461221</v>
       </c>
       <c r="R12" t="n">
-        <v>6776732</v>
+        <v>6776620</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132224221</v>
+        <v>132224248</v>
       </c>
       <c r="B13" t="n">
-        <v>57945</v>
+        <v>79317</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,42 +1918,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461199</v>
+        <v>461144</v>
       </c>
       <c r="R13" t="n">
-        <v>6776717</v>
+        <v>6776647</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2012,41 +2004,40 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132224229</v>
+        <v>132224221</v>
       </c>
       <c r="B14" t="n">
-        <v>8455</v>
+        <v>57945</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2056,10 +2047,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461257</v>
+        <v>461199</v>
       </c>
       <c r="R14" t="n">
-        <v>6776772</v>
+        <v>6776717</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2100,7 +2091,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2119,45 +2109,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132224248</v>
+        <v>132224229</v>
       </c>
       <c r="B15" t="n">
-        <v>79315</v>
+        <v>8455</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461144</v>
+        <v>461257</v>
       </c>
       <c r="R15" t="n">
-        <v>6776647</v>
+        <v>6776772</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2198,6 +2197,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2219,7 +2219,7 @@
         <v>132224245</v>
       </c>
       <c r="B16" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2527,54 +2527,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132224227</v>
+        <v>132224246</v>
       </c>
       <c r="B19" t="n">
-        <v>8455</v>
+        <v>79317</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461226</v>
+        <v>461152</v>
       </c>
       <c r="R19" t="n">
-        <v>6776634</v>
+        <v>6776685</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2615,7 +2606,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2634,45 +2624,54 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132224246</v>
+        <v>132224227</v>
       </c>
       <c r="B20" t="n">
-        <v>79315</v>
+        <v>8455</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461152</v>
+        <v>461226</v>
       </c>
       <c r="R20" t="n">
-        <v>6776685</v>
+        <v>6776634</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2713,6 +2712,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3049,7 +3049,7 @@
         <v>132224250</v>
       </c>
       <c r="B24" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 12829-2026 artfynd.xlsx
+++ b/artfynd/A 12829-2026 artfynd.xlsx
@@ -1907,45 +1907,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132224248</v>
+        <v>132224229</v>
       </c>
       <c r="B13" t="n">
-        <v>79317</v>
+        <v>8455</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461144</v>
+        <v>461257</v>
       </c>
       <c r="R13" t="n">
-        <v>6776647</v>
+        <v>6776772</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1986,6 +1995,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2109,54 +2119,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132224229</v>
+        <v>132224248</v>
       </c>
       <c r="B15" t="n">
-        <v>8455</v>
+        <v>79317</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461257</v>
+        <v>461144</v>
       </c>
       <c r="R15" t="n">
-        <v>6776772</v>
+        <v>6776647</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2197,7 +2198,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 12829-2026 artfynd.xlsx
+++ b/artfynd/A 12829-2026 artfynd.xlsx
@@ -1907,54 +1907,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132224229</v>
+        <v>132224248</v>
       </c>
       <c r="B13" t="n">
-        <v>8455</v>
+        <v>79317</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461257</v>
+        <v>461144</v>
       </c>
       <c r="R13" t="n">
-        <v>6776772</v>
+        <v>6776647</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1995,7 +1986,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2119,45 +2109,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132224248</v>
+        <v>132224229</v>
       </c>
       <c r="B15" t="n">
-        <v>79317</v>
+        <v>8455</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461144</v>
+        <v>461257</v>
       </c>
       <c r="R15" t="n">
-        <v>6776647</v>
+        <v>6776772</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2198,6 +2197,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 12829-2026 artfynd.xlsx
+++ b/artfynd/A 12829-2026 artfynd.xlsx
@@ -1907,45 +1907,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132224248</v>
+        <v>132224229</v>
       </c>
       <c r="B13" t="n">
-        <v>79317</v>
+        <v>8455</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461144</v>
+        <v>461257</v>
       </c>
       <c r="R13" t="n">
-        <v>6776647</v>
+        <v>6776772</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1986,6 +1995,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2004,10 +2014,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132224221</v>
+        <v>132224248</v>
       </c>
       <c r="B14" t="n">
-        <v>57945</v>
+        <v>79317</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2015,42 +2025,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461199</v>
+        <v>461144</v>
       </c>
       <c r="R14" t="n">
-        <v>6776717</v>
+        <v>6776647</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2109,41 +2111,40 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132224229</v>
+        <v>132224221</v>
       </c>
       <c r="B15" t="n">
-        <v>8455</v>
+        <v>57945</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2153,10 +2154,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461257</v>
+        <v>461199</v>
       </c>
       <c r="R15" t="n">
-        <v>6776772</v>
+        <v>6776717</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2197,7 +2198,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2527,45 +2527,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132224246</v>
+        <v>132224227</v>
       </c>
       <c r="B19" t="n">
-        <v>79317</v>
+        <v>8455</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461152</v>
+        <v>461226</v>
       </c>
       <c r="R19" t="n">
-        <v>6776685</v>
+        <v>6776634</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2606,6 +2615,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2624,54 +2634,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132224227</v>
+        <v>132224246</v>
       </c>
       <c r="B20" t="n">
-        <v>8455</v>
+        <v>79317</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461226</v>
+        <v>461152</v>
       </c>
       <c r="R20" t="n">
-        <v>6776634</v>
+        <v>6776685</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2712,7 +2713,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 12829-2026 artfynd.xlsx
+++ b/artfynd/A 12829-2026 artfynd.xlsx
@@ -1699,43 +1699,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132224230</v>
+        <v>132224217</v>
       </c>
       <c r="B11" t="n">
-        <v>8455</v>
+        <v>91913</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1743,10 +1737,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461181</v>
+        <v>461221</v>
       </c>
       <c r="R11" t="n">
-        <v>6776732</v>
+        <v>6776620</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1806,37 +1800,43 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132224217</v>
+        <v>132224230</v>
       </c>
       <c r="B12" t="n">
-        <v>91913</v>
+        <v>8455</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1844,10 +1844,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461221</v>
+        <v>461181</v>
       </c>
       <c r="R12" t="n">
-        <v>6776620</v>
+        <v>6776732</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 12829-2026 artfynd.xlsx
+++ b/artfynd/A 12829-2026 artfynd.xlsx
@@ -2216,45 +2216,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132224245</v>
+        <v>132224231</v>
       </c>
       <c r="B16" t="n">
-        <v>79317</v>
+        <v>8455</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461234</v>
+        <v>461163</v>
       </c>
       <c r="R16" t="n">
-        <v>6776621</v>
+        <v>6776598</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2295,6 +2304,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2313,7 +2323,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132224231</v>
+        <v>132224228</v>
       </c>
       <c r="B17" t="n">
         <v>8455</v>
@@ -2357,10 +2367,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461163</v>
+        <v>461215</v>
       </c>
       <c r="R17" t="n">
-        <v>6776598</v>
+        <v>6776624</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2420,54 +2430,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132224228</v>
+        <v>132224245</v>
       </c>
       <c r="B18" t="n">
-        <v>8455</v>
+        <v>79317</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461215</v>
+        <v>461234</v>
       </c>
       <c r="R18" t="n">
-        <v>6776624</v>
+        <v>6776621</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2508,7 +2509,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2527,54 +2527,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132224227</v>
+        <v>132224246</v>
       </c>
       <c r="B19" t="n">
-        <v>8455</v>
+        <v>79317</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461226</v>
+        <v>461152</v>
       </c>
       <c r="R19" t="n">
-        <v>6776634</v>
+        <v>6776685</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2615,7 +2606,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2634,45 +2624,54 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132224246</v>
+        <v>132224227</v>
       </c>
       <c r="B20" t="n">
-        <v>79317</v>
+        <v>8455</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461152</v>
+        <v>461226</v>
       </c>
       <c r="R20" t="n">
-        <v>6776685</v>
+        <v>6776634</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2713,6 +2712,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 12829-2026 artfynd.xlsx
+++ b/artfynd/A 12829-2026 artfynd.xlsx
@@ -2216,54 +2216,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132224231</v>
+        <v>132224245</v>
       </c>
       <c r="B16" t="n">
-        <v>8455</v>
+        <v>79317</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461163</v>
+        <v>461234</v>
       </c>
       <c r="R16" t="n">
-        <v>6776598</v>
+        <v>6776621</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2304,7 +2295,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2323,7 +2313,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132224228</v>
+        <v>132224231</v>
       </c>
       <c r="B17" t="n">
         <v>8455</v>
@@ -2367,10 +2357,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461215</v>
+        <v>461163</v>
       </c>
       <c r="R17" t="n">
-        <v>6776624</v>
+        <v>6776598</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2430,45 +2420,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132224245</v>
+        <v>132224228</v>
       </c>
       <c r="B18" t="n">
-        <v>79317</v>
+        <v>8455</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461234</v>
+        <v>461215</v>
       </c>
       <c r="R18" t="n">
-        <v>6776621</v>
+        <v>6776624</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2509,6 +2508,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2527,45 +2527,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132224246</v>
+        <v>132224227</v>
       </c>
       <c r="B19" t="n">
-        <v>79317</v>
+        <v>8455</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461152</v>
+        <v>461226</v>
       </c>
       <c r="R19" t="n">
-        <v>6776685</v>
+        <v>6776634</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2606,6 +2615,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2624,54 +2634,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132224227</v>
+        <v>132224246</v>
       </c>
       <c r="B20" t="n">
-        <v>8455</v>
+        <v>79317</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461226</v>
+        <v>461152</v>
       </c>
       <c r="R20" t="n">
-        <v>6776634</v>
+        <v>6776685</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2712,7 +2713,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 12829-2026 artfynd.xlsx
+++ b/artfynd/A 12829-2026 artfynd.xlsx
@@ -1286,7 +1286,7 @@
         <v>132224249</v>
       </c>
       <c r="B7" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>132224220</v>
       </c>
       <c r="B9" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>132224217</v>
       </c>
       <c r="B11" t="n">
-        <v>91913</v>
+        <v>91919</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1907,54 +1907,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132224229</v>
+        <v>132224248</v>
       </c>
       <c r="B13" t="n">
-        <v>8455</v>
+        <v>79319</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461257</v>
+        <v>461144</v>
       </c>
       <c r="R13" t="n">
-        <v>6776772</v>
+        <v>6776647</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1995,7 +1986,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2014,10 +2004,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132224248</v>
+        <v>132224221</v>
       </c>
       <c r="B14" t="n">
-        <v>79317</v>
+        <v>57946</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2025,34 +2015,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461144</v>
+        <v>461199</v>
       </c>
       <c r="R14" t="n">
-        <v>6776647</v>
+        <v>6776717</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2111,40 +2109,41 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132224221</v>
+        <v>132224229</v>
       </c>
       <c r="B15" t="n">
-        <v>57945</v>
+        <v>8455</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2154,10 +2153,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461199</v>
+        <v>461257</v>
       </c>
       <c r="R15" t="n">
-        <v>6776717</v>
+        <v>6776772</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2198,6 +2197,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2219,7 +2219,7 @@
         <v>132224245</v>
       </c>
       <c r="B16" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2527,54 +2527,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132224227</v>
+        <v>132224246</v>
       </c>
       <c r="B19" t="n">
-        <v>8455</v>
+        <v>79319</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461226</v>
+        <v>461152</v>
       </c>
       <c r="R19" t="n">
-        <v>6776634</v>
+        <v>6776685</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2615,7 +2606,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2634,45 +2624,54 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132224246</v>
+        <v>132224227</v>
       </c>
       <c r="B20" t="n">
-        <v>79317</v>
+        <v>8455</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461152</v>
+        <v>461226</v>
       </c>
       <c r="R20" t="n">
-        <v>6776685</v>
+        <v>6776634</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2713,6 +2712,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2734,7 +2734,7 @@
         <v>132224226</v>
       </c>
       <c r="B21" t="n">
-        <v>57139</v>
+        <v>57140</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>132224222</v>
       </c>
       <c r="B22" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>132224223</v>
       </c>
       <c r="B23" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>132224250</v>
       </c>
       <c r="B24" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 12829-2026 artfynd.xlsx
+++ b/artfynd/A 12829-2026 artfynd.xlsx
@@ -2527,45 +2527,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132224246</v>
+        <v>132224227</v>
       </c>
       <c r="B19" t="n">
-        <v>79319</v>
+        <v>8455</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461152</v>
+        <v>461226</v>
       </c>
       <c r="R19" t="n">
-        <v>6776685</v>
+        <v>6776634</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2606,6 +2615,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2624,54 +2634,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132224227</v>
+        <v>132224246</v>
       </c>
       <c r="B20" t="n">
-        <v>8455</v>
+        <v>79319</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461226</v>
+        <v>461152</v>
       </c>
       <c r="R20" t="n">
-        <v>6776634</v>
+        <v>6776685</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2712,7 +2713,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 12829-2026 artfynd.xlsx
+++ b/artfynd/A 12829-2026 artfynd.xlsx
@@ -1286,7 +1286,7 @@
         <v>132224249</v>
       </c>
       <c r="B7" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>132224220</v>
       </c>
       <c r="B9" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>132224217</v>
       </c>
       <c r="B11" t="n">
-        <v>91919</v>
+        <v>91929</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>132224248</v>
       </c>
       <c r="B13" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>132224221</v>
       </c>
       <c r="B14" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2216,45 +2216,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132224245</v>
+        <v>132224231</v>
       </c>
       <c r="B16" t="n">
-        <v>79319</v>
+        <v>8455</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461234</v>
+        <v>461163</v>
       </c>
       <c r="R16" t="n">
-        <v>6776621</v>
+        <v>6776598</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2295,6 +2304,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2313,7 +2323,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132224231</v>
+        <v>132224228</v>
       </c>
       <c r="B17" t="n">
         <v>8455</v>
@@ -2357,10 +2367,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461163</v>
+        <v>461215</v>
       </c>
       <c r="R17" t="n">
-        <v>6776598</v>
+        <v>6776624</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2420,54 +2430,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132224228</v>
+        <v>132224245</v>
       </c>
       <c r="B18" t="n">
-        <v>8455</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461215</v>
+        <v>461234</v>
       </c>
       <c r="R18" t="n">
-        <v>6776624</v>
+        <v>6776621</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2508,7 +2509,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2527,54 +2527,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132224227</v>
+        <v>132224246</v>
       </c>
       <c r="B19" t="n">
-        <v>8455</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461226</v>
+        <v>461152</v>
       </c>
       <c r="R19" t="n">
-        <v>6776634</v>
+        <v>6776685</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2615,7 +2606,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2634,45 +2624,54 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132224246</v>
+        <v>132224227</v>
       </c>
       <c r="B20" t="n">
-        <v>79319</v>
+        <v>8455</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461152</v>
+        <v>461226</v>
       </c>
       <c r="R20" t="n">
-        <v>6776685</v>
+        <v>6776634</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2713,6 +2712,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2734,7 +2734,7 @@
         <v>132224226</v>
       </c>
       <c r="B21" t="n">
-        <v>57140</v>
+        <v>57144</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>132224222</v>
       </c>
       <c r="B22" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>132224223</v>
       </c>
       <c r="B23" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>132224250</v>
       </c>
       <c r="B24" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 12829-2026 artfynd.xlsx
+++ b/artfynd/A 12829-2026 artfynd.xlsx
@@ -1702,7 +1702,7 @@
         <v>132224217</v>
       </c>
       <c r="B11" t="n">
-        <v>91929</v>
+        <v>91930</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1907,45 +1907,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132224248</v>
+        <v>132224229</v>
       </c>
       <c r="B13" t="n">
-        <v>79327</v>
+        <v>8455</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461144</v>
+        <v>461257</v>
       </c>
       <c r="R13" t="n">
-        <v>6776647</v>
+        <v>6776772</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1986,6 +1995,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2004,10 +2014,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132224221</v>
+        <v>132224248</v>
       </c>
       <c r="B14" t="n">
-        <v>57950</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2015,42 +2025,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461199</v>
+        <v>461144</v>
       </c>
       <c r="R14" t="n">
-        <v>6776717</v>
+        <v>6776647</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2109,41 +2111,40 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132224229</v>
+        <v>132224221</v>
       </c>
       <c r="B15" t="n">
-        <v>8455</v>
+        <v>57950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2153,10 +2154,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461257</v>
+        <v>461199</v>
       </c>
       <c r="R15" t="n">
-        <v>6776772</v>
+        <v>6776717</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2197,7 +2198,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2216,54 +2216,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132224231</v>
+        <v>132224245</v>
       </c>
       <c r="B16" t="n">
-        <v>8455</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461163</v>
+        <v>461234</v>
       </c>
       <c r="R16" t="n">
-        <v>6776598</v>
+        <v>6776621</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2304,7 +2295,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2323,7 +2313,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132224228</v>
+        <v>132224231</v>
       </c>
       <c r="B17" t="n">
         <v>8455</v>
@@ -2367,10 +2357,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461215</v>
+        <v>461163</v>
       </c>
       <c r="R17" t="n">
-        <v>6776624</v>
+        <v>6776598</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2430,45 +2420,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132224245</v>
+        <v>132224228</v>
       </c>
       <c r="B18" t="n">
-        <v>79327</v>
+        <v>8455</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461234</v>
+        <v>461215</v>
       </c>
       <c r="R18" t="n">
-        <v>6776621</v>
+        <v>6776624</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2509,6 +2508,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2527,45 +2527,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132224246</v>
+        <v>132224227</v>
       </c>
       <c r="B19" t="n">
-        <v>79327</v>
+        <v>8455</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461152</v>
+        <v>461226</v>
       </c>
       <c r="R19" t="n">
-        <v>6776685</v>
+        <v>6776634</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2606,6 +2615,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2624,54 +2634,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132224227</v>
+        <v>132224246</v>
       </c>
       <c r="B20" t="n">
-        <v>8455</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461226</v>
+        <v>461152</v>
       </c>
       <c r="R20" t="n">
-        <v>6776634</v>
+        <v>6776685</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2712,7 +2713,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 12829-2026 artfynd.xlsx
+++ b/artfynd/A 12829-2026 artfynd.xlsx
@@ -1907,54 +1907,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132224229</v>
+        <v>132224248</v>
       </c>
       <c r="B13" t="n">
-        <v>8455</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461257</v>
+        <v>461144</v>
       </c>
       <c r="R13" t="n">
-        <v>6776772</v>
+        <v>6776647</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1995,7 +1986,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2014,45 +2004,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132224248</v>
+        <v>132224229</v>
       </c>
       <c r="B14" t="n">
-        <v>79327</v>
+        <v>8455</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461144</v>
+        <v>461257</v>
       </c>
       <c r="R14" t="n">
-        <v>6776647</v>
+        <v>6776772</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2093,6 +2092,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2527,54 +2527,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132224227</v>
+        <v>132224246</v>
       </c>
       <c r="B19" t="n">
-        <v>8455</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461226</v>
+        <v>461152</v>
       </c>
       <c r="R19" t="n">
-        <v>6776634</v>
+        <v>6776685</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2615,7 +2606,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2634,45 +2624,54 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132224246</v>
+        <v>132224227</v>
       </c>
       <c r="B20" t="n">
-        <v>79327</v>
+        <v>8455</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461152</v>
+        <v>461226</v>
       </c>
       <c r="R20" t="n">
-        <v>6776685</v>
+        <v>6776634</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2713,6 +2712,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 12829-2026 artfynd.xlsx
+++ b/artfynd/A 12829-2026 artfynd.xlsx
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132224248</v>
+        <v>132224221</v>
       </c>
       <c r="B13" t="n">
-        <v>79327</v>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,34 +1918,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461144</v>
+        <v>461199</v>
       </c>
       <c r="R13" t="n">
-        <v>6776647</v>
+        <v>6776717</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2111,10 +2119,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132224221</v>
+        <v>132224248</v>
       </c>
       <c r="B15" t="n">
-        <v>57950</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2122,42 +2130,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461199</v>
+        <v>461144</v>
       </c>
       <c r="R15" t="n">
-        <v>6776717</v>
+        <v>6776647</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 12829-2026 artfynd.xlsx
+++ b/artfynd/A 12829-2026 artfynd.xlsx
@@ -2216,45 +2216,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132224245</v>
+        <v>132224231</v>
       </c>
       <c r="B16" t="n">
-        <v>79327</v>
+        <v>8455</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461234</v>
+        <v>461163</v>
       </c>
       <c r="R16" t="n">
-        <v>6776621</v>
+        <v>6776598</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2295,6 +2304,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2313,7 +2323,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132224231</v>
+        <v>132224228</v>
       </c>
       <c r="B17" t="n">
         <v>8455</v>
@@ -2357,10 +2367,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461163</v>
+        <v>461215</v>
       </c>
       <c r="R17" t="n">
-        <v>6776598</v>
+        <v>6776624</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2420,54 +2430,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132224228</v>
+        <v>132224245</v>
       </c>
       <c r="B18" t="n">
-        <v>8455</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461215</v>
+        <v>461234</v>
       </c>
       <c r="R18" t="n">
-        <v>6776624</v>
+        <v>6776621</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2508,7 +2509,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 12829-2026 artfynd.xlsx
+++ b/artfynd/A 12829-2026 artfynd.xlsx
@@ -1286,7 +1286,7 @@
         <v>132224249</v>
       </c>
       <c r="B7" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>132224220</v>
       </c>
       <c r="B9" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1699,37 +1699,43 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132224217</v>
+        <v>132224230</v>
       </c>
       <c r="B11" t="n">
-        <v>91930</v>
+        <v>8455</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1737,10 +1743,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461221</v>
+        <v>461181</v>
       </c>
       <c r="R11" t="n">
-        <v>6776620</v>
+        <v>6776732</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1800,43 +1806,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132224230</v>
+        <v>132224217</v>
       </c>
       <c r="B12" t="n">
-        <v>8455</v>
+        <v>91931</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1844,10 +1844,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461181</v>
+        <v>461221</v>
       </c>
       <c r="R12" t="n">
-        <v>6776732</v>
+        <v>6776620</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132224221</v>
+        <v>132224248</v>
       </c>
       <c r="B13" t="n">
-        <v>57950</v>
+        <v>79328</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,42 +1918,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461199</v>
+        <v>461144</v>
       </c>
       <c r="R13" t="n">
-        <v>6776717</v>
+        <v>6776647</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2012,41 +2004,40 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132224229</v>
+        <v>132224221</v>
       </c>
       <c r="B14" t="n">
-        <v>8455</v>
+        <v>57951</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2056,10 +2047,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461257</v>
+        <v>461199</v>
       </c>
       <c r="R14" t="n">
-        <v>6776772</v>
+        <v>6776717</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2100,7 +2091,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2119,45 +2109,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132224248</v>
+        <v>132224229</v>
       </c>
       <c r="B15" t="n">
-        <v>79327</v>
+        <v>8455</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461144</v>
+        <v>461257</v>
       </c>
       <c r="R15" t="n">
-        <v>6776647</v>
+        <v>6776772</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2198,6 +2197,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2216,54 +2216,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132224231</v>
+        <v>132224245</v>
       </c>
       <c r="B16" t="n">
-        <v>8455</v>
+        <v>79328</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461163</v>
+        <v>461234</v>
       </c>
       <c r="R16" t="n">
-        <v>6776598</v>
+        <v>6776621</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2304,7 +2295,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2323,7 +2313,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132224228</v>
+        <v>132224231</v>
       </c>
       <c r="B17" t="n">
         <v>8455</v>
@@ -2367,10 +2357,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461215</v>
+        <v>461163</v>
       </c>
       <c r="R17" t="n">
-        <v>6776624</v>
+        <v>6776598</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2430,45 +2420,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132224245</v>
+        <v>132224228</v>
       </c>
       <c r="B18" t="n">
-        <v>79327</v>
+        <v>8455</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461234</v>
+        <v>461215</v>
       </c>
       <c r="R18" t="n">
-        <v>6776621</v>
+        <v>6776624</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2509,6 +2508,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2530,7 +2530,7 @@
         <v>132224246</v>
       </c>
       <c r="B19" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>132224226</v>
       </c>
       <c r="B21" t="n">
-        <v>57144</v>
+        <v>57145</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>132224222</v>
       </c>
       <c r="B22" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>132224223</v>
       </c>
       <c r="B23" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>132224250</v>
       </c>
       <c r="B24" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 12829-2026 artfynd.xlsx
+++ b/artfynd/A 12829-2026 artfynd.xlsx
@@ -1699,43 +1699,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132224230</v>
+        <v>132224217</v>
       </c>
       <c r="B11" t="n">
-        <v>8455</v>
+        <v>91933</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1743,10 +1737,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461181</v>
+        <v>461221</v>
       </c>
       <c r="R11" t="n">
-        <v>6776732</v>
+        <v>6776620</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1806,37 +1800,43 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132224217</v>
+        <v>132224230</v>
       </c>
       <c r="B12" t="n">
-        <v>91931</v>
+        <v>8455</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1844,10 +1844,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461221</v>
+        <v>461181</v>
       </c>
       <c r="R12" t="n">
-        <v>6776620</v>
+        <v>6776732</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 12829-2026 artfynd.xlsx
+++ b/artfynd/A 12829-2026 artfynd.xlsx
@@ -1286,7 +1286,7 @@
         <v>132224249</v>
       </c>
       <c r="B7" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>132224217</v>
       </c>
       <c r="B11" t="n">
-        <v>91933</v>
+        <v>91934</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1907,45 +1907,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132224248</v>
+        <v>132224229</v>
       </c>
       <c r="B13" t="n">
-        <v>79328</v>
+        <v>8455</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461144</v>
+        <v>461257</v>
       </c>
       <c r="R13" t="n">
-        <v>6776647</v>
+        <v>6776772</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1986,6 +1995,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2004,10 +2014,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132224221</v>
+        <v>132224248</v>
       </c>
       <c r="B14" t="n">
-        <v>57951</v>
+        <v>79329</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2015,42 +2025,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461199</v>
+        <v>461144</v>
       </c>
       <c r="R14" t="n">
-        <v>6776717</v>
+        <v>6776647</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2109,41 +2111,40 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132224229</v>
+        <v>132224221</v>
       </c>
       <c r="B15" t="n">
-        <v>8455</v>
+        <v>57951</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2153,10 +2154,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461257</v>
+        <v>461199</v>
       </c>
       <c r="R15" t="n">
-        <v>6776772</v>
+        <v>6776717</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2197,7 +2198,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2219,7 +2219,7 @@
         <v>132224245</v>
       </c>
       <c r="B16" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>132224246</v>
       </c>
       <c r="B19" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>132224250</v>
       </c>
       <c r="B24" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 12829-2026 artfynd.xlsx
+++ b/artfynd/A 12829-2026 artfynd.xlsx
@@ -1699,37 +1699,43 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132224217</v>
+        <v>132224230</v>
       </c>
       <c r="B11" t="n">
-        <v>91934</v>
+        <v>8455</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1737,10 +1743,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461221</v>
+        <v>461181</v>
       </c>
       <c r="R11" t="n">
-        <v>6776620</v>
+        <v>6776732</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1800,43 +1806,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132224230</v>
+        <v>132224217</v>
       </c>
       <c r="B12" t="n">
-        <v>8455</v>
+        <v>91934</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1844,10 +1844,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461181</v>
+        <v>461221</v>
       </c>
       <c r="R12" t="n">
-        <v>6776732</v>
+        <v>6776620</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,54 +1907,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132224229</v>
+        <v>132224248</v>
       </c>
       <c r="B13" t="n">
-        <v>8455</v>
+        <v>79329</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461257</v>
+        <v>461144</v>
       </c>
       <c r="R13" t="n">
-        <v>6776772</v>
+        <v>6776647</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1995,7 +1986,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2014,10 +2004,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132224248</v>
+        <v>132224221</v>
       </c>
       <c r="B14" t="n">
-        <v>79329</v>
+        <v>57951</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2025,34 +2015,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461144</v>
+        <v>461199</v>
       </c>
       <c r="R14" t="n">
-        <v>6776647</v>
+        <v>6776717</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2111,40 +2109,41 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132224221</v>
+        <v>132224229</v>
       </c>
       <c r="B15" t="n">
-        <v>57951</v>
+        <v>8455</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2154,10 +2153,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461199</v>
+        <v>461257</v>
       </c>
       <c r="R15" t="n">
-        <v>6776717</v>
+        <v>6776772</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2198,6 +2197,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 12829-2026 artfynd.xlsx
+++ b/artfynd/A 12829-2026 artfynd.xlsx
@@ -1699,43 +1699,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132224230</v>
+        <v>132224217</v>
       </c>
       <c r="B11" t="n">
-        <v>8455</v>
+        <v>91934</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1743,10 +1737,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461181</v>
+        <v>461221</v>
       </c>
       <c r="R11" t="n">
-        <v>6776732</v>
+        <v>6776620</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1806,37 +1800,43 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132224217</v>
+        <v>132224230</v>
       </c>
       <c r="B12" t="n">
-        <v>91934</v>
+        <v>8455</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1844,10 +1844,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461221</v>
+        <v>461181</v>
       </c>
       <c r="R12" t="n">
-        <v>6776620</v>
+        <v>6776732</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,45 +1907,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132224248</v>
+        <v>132224229</v>
       </c>
       <c r="B13" t="n">
-        <v>79329</v>
+        <v>8455</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461144</v>
+        <v>461257</v>
       </c>
       <c r="R13" t="n">
-        <v>6776647</v>
+        <v>6776772</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1986,6 +1995,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2109,54 +2119,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132224229</v>
+        <v>132224248</v>
       </c>
       <c r="B15" t="n">
-        <v>8455</v>
+        <v>79329</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461257</v>
+        <v>461144</v>
       </c>
       <c r="R15" t="n">
-        <v>6776772</v>
+        <v>6776647</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2197,7 +2198,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2216,45 +2216,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132224245</v>
+        <v>132224231</v>
       </c>
       <c r="B16" t="n">
-        <v>79329</v>
+        <v>8455</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461234</v>
+        <v>461163</v>
       </c>
       <c r="R16" t="n">
-        <v>6776621</v>
+        <v>6776598</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2295,6 +2304,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2313,7 +2323,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132224231</v>
+        <v>132224228</v>
       </c>
       <c r="B17" t="n">
         <v>8455</v>
@@ -2357,10 +2367,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461163</v>
+        <v>461215</v>
       </c>
       <c r="R17" t="n">
-        <v>6776598</v>
+        <v>6776624</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2420,54 +2430,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132224228</v>
+        <v>132224245</v>
       </c>
       <c r="B18" t="n">
-        <v>8455</v>
+        <v>79329</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461215</v>
+        <v>461234</v>
       </c>
       <c r="R18" t="n">
-        <v>6776624</v>
+        <v>6776621</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2508,7 +2509,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 12829-2026 artfynd.xlsx
+++ b/artfynd/A 12829-2026 artfynd.xlsx
@@ -1907,54 +1907,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132224229</v>
+        <v>132224248</v>
       </c>
       <c r="B13" t="n">
-        <v>8455</v>
+        <v>79329</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461257</v>
+        <v>461144</v>
       </c>
       <c r="R13" t="n">
-        <v>6776772</v>
+        <v>6776647</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1995,7 +1986,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2119,45 +2109,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132224248</v>
+        <v>132224229</v>
       </c>
       <c r="B15" t="n">
-        <v>79329</v>
+        <v>8455</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461144</v>
+        <v>461257</v>
       </c>
       <c r="R15" t="n">
-        <v>6776647</v>
+        <v>6776772</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2198,6 +2197,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2216,54 +2216,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132224231</v>
+        <v>132224245</v>
       </c>
       <c r="B16" t="n">
-        <v>8455</v>
+        <v>79329</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461163</v>
+        <v>461234</v>
       </c>
       <c r="R16" t="n">
-        <v>6776598</v>
+        <v>6776621</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2304,7 +2295,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2323,7 +2313,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132224228</v>
+        <v>132224231</v>
       </c>
       <c r="B17" t="n">
         <v>8455</v>
@@ -2367,10 +2357,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461215</v>
+        <v>461163</v>
       </c>
       <c r="R17" t="n">
-        <v>6776624</v>
+        <v>6776598</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2430,45 +2420,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132224245</v>
+        <v>132224228</v>
       </c>
       <c r="B18" t="n">
-        <v>79329</v>
+        <v>8455</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461234</v>
+        <v>461215</v>
       </c>
       <c r="R18" t="n">
-        <v>6776621</v>
+        <v>6776624</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2509,6 +2508,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2527,45 +2527,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132224246</v>
+        <v>132224227</v>
       </c>
       <c r="B19" t="n">
-        <v>79329</v>
+        <v>8455</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461152</v>
+        <v>461226</v>
       </c>
       <c r="R19" t="n">
-        <v>6776685</v>
+        <v>6776634</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2606,6 +2615,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2624,54 +2634,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132224227</v>
+        <v>132224246</v>
       </c>
       <c r="B20" t="n">
-        <v>8455</v>
+        <v>79329</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461226</v>
+        <v>461152</v>
       </c>
       <c r="R20" t="n">
-        <v>6776634</v>
+        <v>6776685</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2712,7 +2713,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 12829-2026 artfynd.xlsx
+++ b/artfynd/A 12829-2026 artfynd.xlsx
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132224248</v>
+        <v>132224221</v>
       </c>
       <c r="B13" t="n">
-        <v>79329</v>
+        <v>57951</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,34 +1918,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461144</v>
+        <v>461199</v>
       </c>
       <c r="R13" t="n">
-        <v>6776647</v>
+        <v>6776717</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2004,40 +2012,41 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132224221</v>
+        <v>132224229</v>
       </c>
       <c r="B14" t="n">
-        <v>57951</v>
+        <v>8455</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2047,10 +2056,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461199</v>
+        <v>461257</v>
       </c>
       <c r="R14" t="n">
-        <v>6776717</v>
+        <v>6776772</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2091,6 +2100,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2109,54 +2119,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132224229</v>
+        <v>132224248</v>
       </c>
       <c r="B15" t="n">
-        <v>8455</v>
+        <v>79329</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Drittjärnberg, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461257</v>
+        <v>461144</v>
       </c>
       <c r="R15" t="n">
-        <v>6776772</v>
+        <v>6776647</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2197,7 +2198,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
